--- a/data/trending_integrated_20261027_12.xlsx
+++ b/data/trending_integrated_20261027_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41776575380</v>
+        <v>41782290010</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18709123205</v>
+        <v>18712387395</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 나무가의 독점 공급 관련 호재 부각. 3분기 어닝 서프라이즈 가능성 언급.</t>
+          <t>휴머노이드 로봇 '아틀라스' 메인 카메라 단독 공급망 확정, LG이노텍 제치고 채택. 3분기 어닝 서프라이즈 및 텐버거 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['아틀라스', '휴머노이드', '로봇']</t>
+          <t>['아틀라스', '로봇', '3D센싱']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21000</v>
+        <v>2270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.24%</t>
+          <t>'+11.55%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K4" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L4" t="n">
-        <v>22450</v>
+        <v>2280</v>
       </c>
       <c r="M4" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N4" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>61975562115</v>
+        <v>27647475720</v>
       </c>
       <c r="P4" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q4" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R4" t="n">
-        <v>7000</v>
+        <v>-89000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브릴스, 로봇 기업으로 빅웨이브 기대감. 기술 특례 상장 기업.</t>
+          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '빅웨이브', '기술특례']</t>
+          <t>['로보월드', '변동성', '개미털기']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,191 +832,191 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1345000</v>
+        <v>20850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.49%</t>
+          <t>'+9.45%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>448</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>1433</v>
+        <v>128</v>
       </c>
       <c r="H5" t="n">
-        <v>48.66</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1275000</v>
+        <v>19050</v>
       </c>
       <c r="K5" t="n">
-        <v>1346000</v>
+        <v>19450</v>
       </c>
       <c r="L5" t="n">
-        <v>1381000</v>
+        <v>22450</v>
       </c>
       <c r="M5" t="n">
-        <v>1341000</v>
+        <v>18430</v>
       </c>
       <c r="N5" t="n">
-        <v>48.69</v>
+        <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>2268080544500</v>
+        <v>62663380340</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>62100</v>
       </c>
       <c r="Q5" t="n">
-        <v>501000</v>
+        <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>174000</v>
+        <v>7000</v>
       </c>
       <c r="S5" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 발표 후 매수 권고 및 앤트로픽 관련 HBM 수요 언급. 외국인, 기관의 쌍끌이 매수세가 유입되었으나, 시장 전반의 대세 하락장 우려와 함께 단기적 상승 후 하락 가능성도 제기됨.</t>
+          <t>브릴스, 로봇 기업으로 빅웨이브 기대감. 기술 특례 상장 기업.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적발표', 'HBM', '쌍끌이매수']</t>
+          <t>['로봇', '빅웨이브', '기술특례']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2145</v>
+        <v>1348000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.41%</t>
+          <t>'+5.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>444</v>
       </c>
       <c r="G6" t="n">
-        <v>130</v>
+        <v>1469</v>
       </c>
       <c r="H6" t="n">
-        <v>4.89</v>
+        <v>48.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2035</v>
+        <v>1275000</v>
       </c>
       <c r="K6" t="n">
-        <v>2035</v>
+        <v>1346000</v>
       </c>
       <c r="L6" t="n">
-        <v>2210</v>
+        <v>1381000</v>
       </c>
       <c r="M6" t="n">
-        <v>1953</v>
+        <v>1341000</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>23958147787</v>
+        <v>2311888364500</v>
       </c>
       <c r="P6" t="n">
-        <v>4980</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>749</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>-89000</v>
+        <v>174000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
+          <t>실적 발표 후 매수 의견, 앤트로픽 상장 및 TCU 구매 약정 관련 언급. 외국인, 기관 동반 매수세 관측.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로보월드', '변동성', '개미털기']</t>
+          <t>['실적발표', '앤트로픽', 'TCU']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
         <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="H7" t="n">
         <v>40.44</v>
@@ -1070,7 +1070,7 @@
         <v>40.39</v>
       </c>
       <c r="O7" t="n">
-        <v>186605410350</v>
+        <v>188901628950</v>
       </c>
       <c r="P7" t="n">
         <v>67300</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>221750</v>
+        <v>222000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.11%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="G8" t="n">
-        <v>1365</v>
+        <v>1347</v>
       </c>
       <c r="H8" t="n">
         <v>46.1</v>
@@ -1162,7 +1162,7 @@
         <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>1645267526500</v>
+        <v>1668624378250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대통령 일정 관련 언급과 함께 공매도 세력에 대한 부정적 전망 제시. SK하이닉스 ETF의 미국 증시 퇴장 및 HBM 부족 관련 뉴스가 위험 요인으로 언급되었으며, 20만원 바닥 후 상승 기대와 외인 매도세 시작에 대한 혼조세를 보임.</t>
+          <t>트럼프 외교 관련 언급, 공매도 관련 부정적 전망, SK하이닉스 ETF 퇴장 및 HBM 부족 관련 뉴스 언급. 주가 하락 및 외인 매도세 관측.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14690</v>
+        <v>14700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.31%</t>
+          <t>'+3.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="H9" t="n">
         <v>10.02</v>
@@ -1254,7 +1254,7 @@
         <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>33484509635</v>
+        <v>33708524315</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 영업이익 223% 증가 확인. 외국인, 기관 프로그램 매수세 지속 관찰.</t>
+          <t>3분기 영업이익 223% 폭증 실적 발표 기반 긍정적 전망. 외국인, 기관 프로그램 매수 지속 및 공매도, 대차 물량 감소 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익', '실적발표', '외국인기관']</t>
+          <t>['영업이익', '실적발표', '외국인매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13780</v>
+        <v>13800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>51953001430</v>
+        <v>52167589180</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16520</v>
+        <v>16470</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>30558914295</v>
+        <v>31112579360</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26750</v>
+        <v>26650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+0.57%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H12" t="n">
         <v>12.32</v>
@@ -1530,7 +1530,7 @@
         <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>36669249800</v>
+        <v>36994794425</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14550</v>
+        <v>14490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F13" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>69681548395</v>
+        <v>70099010575</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33900</v>
+        <v>34250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.12%</t>
+          <t>'-6.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
         <v>190</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>92507856050</v>
+        <v>93377353000</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>

--- a/data/trending_integrated_20261027_12.xlsx
+++ b/data/trending_integrated_20261027_12.xlsx
@@ -578,10 +578,10 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>64</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41782290010</v>
+        <v>41798515760</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18712387395</v>
+        <v>18712900095</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2270</v>
+        <v>20600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.55%</t>
+          <t>'+8.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H4" t="n">
-        <v>4.89</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2035</v>
+        <v>19050</v>
       </c>
       <c r="K4" t="n">
-        <v>2035</v>
+        <v>19450</v>
       </c>
       <c r="L4" t="n">
-        <v>2280</v>
+        <v>22450</v>
       </c>
       <c r="M4" t="n">
-        <v>1953</v>
+        <v>18430</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>27647475720</v>
+        <v>63268665440</v>
       </c>
       <c r="P4" t="n">
-        <v>4980</v>
+        <v>62100</v>
       </c>
       <c r="Q4" t="n">
-        <v>749</v>
+        <v>14600</v>
       </c>
       <c r="R4" t="n">
-        <v>-89000</v>
+        <v>7000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
+          <t>로봇 기업 빅웨이브 관련 기대감 있으나, 상승 여력 및 주가 흐름에 대한 불확실성 존재. 보호예수 물량 및 단타 매매 성향 강함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로보월드', '변동성', '개미털기']</t>
+          <t>['로봇 기업', '상승 여력', '보호예수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20850</v>
+        <v>2195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.45%</t>
+          <t>'+7.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K5" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L5" t="n">
-        <v>22450</v>
+        <v>2285</v>
       </c>
       <c r="M5" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N5" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>62663380340</v>
+        <v>33024971086</v>
       </c>
       <c r="P5" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q5" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R5" t="n">
-        <v>7000</v>
+        <v>-89000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>브릴스, 로봇 기업으로 빅웨이브 기대감. 기술 특례 상장 기업.</t>
+          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', '빅웨이브', '기술특례']</t>
+          <t>['로보월드', '변동성', '개미털기']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="G6" t="n">
-        <v>1469</v>
+        <v>1503</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2311888364500</v>
+        <v>2365783346000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 후 매수 의견, 앤트로픽 상장 및 TCU 구매 약정 관련 언급. 외국인, 기관 동반 매수세 관측.</t>
+          <t>실적 발표 후 매수 관망세. 앤트로픽 상장 신청서상 HBM 구매 약정 확인. 외국인, 기관 쌍끌이 매수세 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적발표', '앤트로픽', 'TCU']</t>
+          <t>['실적 발표', 'HBM 구매 약정', '쌍끌이 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62400</v>
+        <v>222000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>460</v>
       </c>
       <c r="G7" t="n">
-        <v>755</v>
+        <v>1322</v>
       </c>
       <c r="H7" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K7" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L7" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M7" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N7" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>188901628950</v>
+        <v>1691863141500</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>195000</v>
+        <v>1019000</v>
       </c>
       <c r="S7" t="n">
-        <v>15000</v>
+        <v>432000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>중동발 지정학적 리스크 속에서도 삼성그룹주 중 저평가 메리트 부각. MSCI 종목 편입 기대감과 함께 대형 수주 공시 가능성이 거론되며, 외인 매수세 유입 및 야간 선물 급등 등 긍정적 시그널이 다수 관찰됨.</t>
+          <t>미국 증시 SK하이닉스 ETF 퇴장 및 HBM 부족 관련 뉴스에도 불구하고 20만원 바닥 다진 후 상승 전망. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['저평가', '대형수주', 'MSCI']</t>
+          <t>['SK하이닉스 ETF', 'HBM 부족', '외국인 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>222000</v>
+        <v>62100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+3.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>123</v>
       </c>
       <c r="F8" t="n">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>1347</v>
+        <v>761</v>
       </c>
       <c r="H8" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K8" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L8" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>221000</v>
+        <v>60100</v>
       </c>
       <c r="N8" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>1668624378250</v>
+        <v>192770906450</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>1019000</v>
+        <v>195000</v>
       </c>
       <c r="S8" t="n">
-        <v>432000</v>
+        <v>15000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>트럼프 외교 관련 언급, 공매도 관련 부정적 전망, SK하이닉스 ETF 퇴장 및 HBM 부족 관련 뉴스 언급. 주가 하락 및 외인 매도세 관측.</t>
+          <t>중동발 지정학적 리스크 속에서도 삼성그룹주 중 저평가 메리트 부각. MSCI 종목 편입 기대감과 함께 대형 수주 공시 가능성이 거론되며, 외인 매수세 유입 및 야간 선물 급등 등 긍정적 시그널이 다수 관찰됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', 'HBM', '외인매도']</t>
+          <t>['저평가', '대형수주', 'MSCI']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14700</v>
+        <v>14630</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.38%</t>
+          <t>'+2.88%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="H9" t="n">
         <v>10.02</v>
@@ -1254,7 +1254,7 @@
         <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>33708524315</v>
+        <v>34086207420</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 영업이익 223% 폭증 실적 발표 기반 긍정적 전망. 외국인, 기관 프로그램 매수 지속 및 공매도, 대차 물량 감소 기대.</t>
+          <t>3분기 영업이익 223% 폭증 실적 발표. 외국인, 기관 프로그램 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익', '실적발표', '외국인매수']</t>
+          <t>['영업이익 폭증', '실적 발표', '기관 매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13800</v>
+        <v>13720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>52167589180</v>
+        <v>53142189170</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1406,13 +1406,13 @@
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
         <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>31112579360</v>
+        <v>31446591980</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26650</v>
+        <v>26625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.57%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H12" t="n">
         <v>12.32</v>
@@ -1530,7 +1530,7 @@
         <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>36994794425</v>
+        <v>37294249075</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14490</v>
+        <v>14580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13" t="n">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>70099010575</v>
+        <v>70970314485</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>본격적인 상승 추세 진입 및 거래대금 폭증, 공매도 숏커버링 발생. 루닛스코프, AI 신약 개발 활용 등 기술적 확장성과 성장성이 부각되며, 해외 수출 및 파트너십 확대가 긍정적 요인으로 분석됨.</t>
+          <t>루닛스코프, AI 신약 개발 활용 사례 증가. 해외 수출 확대 및 성장성, 확장성 확고. 외국인·기관 동시 순매수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI신약개발', '숏커버링', '해외수출']</t>
+          <t>['루닛스코프', 'AI 신약 개발', '외국인·기관 순매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34250</v>
+        <v>34350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.16%</t>
+          <t>'-5.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>93377353000</v>
+        <v>94288712700</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>

--- a/data/trending_integrated_20261027_12.xlsx
+++ b/data/trending_integrated_20261027_12.xlsx
@@ -578,10 +578,10 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>64</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41798515760</v>
+        <v>41844960980</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18712900095</v>
+        <v>18712917185</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20600</v>
+        <v>2250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.14%</t>
+          <t>'+10.57%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K4" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L4" t="n">
-        <v>22450</v>
+        <v>2300</v>
       </c>
       <c r="M4" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N4" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>63268665440</v>
+        <v>39089702984</v>
       </c>
       <c r="P4" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q4" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R4" t="n">
-        <v>7000</v>
+        <v>-89000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 기업 빅웨이브 관련 기대감 있으나, 상승 여력 및 주가 흐름에 대한 불확실성 존재. 보호예수 물량 및 단타 매매 성향 강함.</t>
+          <t>스마트 팩토리 및 로봇 관련 사업 기대감 속 변동성 장세. 개미 털기 및 주가 관리 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇 기업', '상승 여력', '보호예수']</t>
+          <t>['스마트팩토리', '로봇', '개미털기']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2195</v>
+        <v>21050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.86%</t>
+          <t>'+10.50%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H5" t="n">
-        <v>4.89</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,60 +871,60 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2035</v>
+        <v>19050</v>
       </c>
       <c r="K5" t="n">
-        <v>2035</v>
+        <v>19450</v>
       </c>
       <c r="L5" t="n">
-        <v>2285</v>
+        <v>22450</v>
       </c>
       <c r="M5" t="n">
-        <v>1953</v>
+        <v>18430</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>33024971086</v>
+        <v>64980672965</v>
       </c>
       <c r="P5" t="n">
-        <v>4980</v>
+        <v>62100</v>
       </c>
       <c r="Q5" t="n">
-        <v>749</v>
+        <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>-89000</v>
+        <v>7000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
+          <t>로봇 기업 빅웨이브 관련 기대감 있으나, 상승 여력 및 주가 흐름에 대한 불확실성 존재. 보호예수 물량 및 단타 매매 성향 강함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로보월드', '변동성', '개미털기']</t>
+          <t>['로봇 기업', '상승 여력', '보호예수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1348000</v>
+        <v>1351000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.73%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="G6" t="n">
-        <v>1503</v>
+        <v>1528</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2365783346000</v>
+        <v>2426483646000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 후 매수 관망세. 앤트로픽 상장 신청서상 HBM 구매 약정 확인. 외국인, 기관 쌍끌이 매수세 관찰.</t>
+          <t>실적 발표 이후 주가 상승 기대감 있으나, 단기 차익 실현 및 관망세 존재. 엔트로픽 상장 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 발표', 'HBM 구매 약정', '쌍끌이 매수']</t>
+          <t>['실적발표', '엔트로픽', '주주환원']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222000</v>
+        <v>62500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.52%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="G7" t="n">
-        <v>1322</v>
+        <v>783</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K7" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L7" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M7" t="n">
-        <v>221000</v>
+        <v>60100</v>
       </c>
       <c r="N7" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O7" t="n">
-        <v>1691863141500</v>
+        <v>195820599050</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>1019000</v>
+        <v>195000</v>
       </c>
       <c r="S7" t="n">
-        <v>432000</v>
+        <v>15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 증시 SK하이닉스 ETF 퇴장 및 HBM 부족 관련 뉴스에도 불구하고 20만원 바닥 다진 후 상승 전망. 외국인 매도세 관찰.</t>
+          <t>중동발 지정학적 리스크 속에서도 삼성그룹주 중 저평가 메리트 부각. MSCI 종목 편입 기대감과 함께 대형 수주 공시 가능성이 거론되며, 외인 매수세 유입 및 야간 선물 급등 등 긍정적 시그널이 다수 관찰됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SK하이닉스 ETF', 'HBM 부족', '외국인 매도']</t>
+          <t>['저평가', '대형수주', 'MSCI']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62100</v>
+        <v>222000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.85%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="G8" t="n">
-        <v>761</v>
+        <v>1327</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>192770906450</v>
+        <v>1737083094250</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>195000</v>
+        <v>1019000</v>
       </c>
       <c r="S8" t="n">
-        <v>15000</v>
+        <v>432000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동발 지정학적 리스크 속에서도 삼성그룹주 중 저평가 메리트 부각. MSCI 종목 편입 기대감과 함께 대형 수주 공시 가능성이 거론되며, 외인 매수세 유입 및 야간 선물 급등 등 긍정적 시그널이 다수 관찰됨.</t>
+          <t>반도체 업황 개선 기대 속 외국인 매도세 지속. 일부 HBM 부족 우려 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['저평가', '대형수주', 'MSCI']</t>
+          <t>['반도체', 'HBM', '외국인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14630</v>
+        <v>14640</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.88%</t>
+          <t>'+2.95%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H9" t="n">
         <v>10.02</v>
@@ -1254,7 +1254,7 @@
         <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>34086207420</v>
+        <v>34421633620</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13720</v>
+        <v>13690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.32%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1340,13 +1340,13 @@
         <v>14410</v>
       </c>
       <c r="M10" t="n">
-        <v>13710</v>
+        <v>13660</v>
       </c>
       <c r="N10" t="n">
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>53142189170</v>
+        <v>54668830700</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16470</v>
+        <v>16490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+1.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>31446591980</v>
+        <v>32209485060</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26625</v>
+        <v>26550</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H12" t="n">
         <v>12.32</v>
@@ -1530,7 +1530,7 @@
         <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>37294249075</v>
+        <v>38150928600</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14580</v>
+        <v>14450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G13" t="n">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>70970314485</v>
+        <v>71505295565</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>루닛스코프, AI 신약 개발 활용 사례 증가. 해외 수출 확대 및 성장성, 확장성 확고. 외국인·기관 동시 순매수.</t>
+          <t>의료 AI 대장주로서 성장성 및 확장성 부각. 해외 수출 및 신약 개발 활용 등 긍정적 분석. 연기금 매수세 및 공매도 숏커버링 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['루닛스코프', 'AI 신약 개발', '외국인·기관 순매수']</t>
+          <t>['의료AI', '성장성', '신약개발']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34350</v>
+        <v>34250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.89%</t>
+          <t>'-6.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>94288712700</v>
+        <v>95455327925</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>분기 실적 부진 및 컨센서스 하회에 따른 급락세. 외인, 프로그램 매도세가 집중되며 종가 하한가를 기록. 일시적 상승 후 물량 던지기 패턴이 관찰되며, 추가 하락 가능성이 높게 점쳐짐.</t>
+          <t>영업이익 증가에도 불구하고 주가 하락 및 개인 투자자들의 불안감 표출. 하락 이유에 대한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적부진', '컨센서스하회', '하한가']</t>
+          <t>['영업이익', '주가하락', '개미']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_12.xlsx
+++ b/data/trending_integrated_20261027_12.xlsx
@@ -581,10 +581,10 @@
         <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41844960980</v>
+        <v>41868943430</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18712917185</v>
+        <v>18723239545</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2250</v>
+        <v>2235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.57%</t>
+          <t>'+9.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
         <v>149</v>
@@ -794,7 +794,7 @@
         <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>39089702984</v>
+        <v>41593646207</v>
       </c>
       <c r="P4" t="n">
         <v>4980</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스마트 팩토리 및 로봇 관련 사업 기대감 속 변동성 장세. 개미 털기 및 주가 관리 언급.</t>
+          <t>로봇 관련주로 스마트 팩토리 및 자동화 테마 언급. 2026 로보월드 행사 기대감 있으나, 개미 털기 및 변동성 수반 장세 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스마트팩토리', '로봇', '개미털기']</t>
+          <t>['스마트팩토리', '로보월드', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21050</v>
+        <v>20900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.50%</t>
+          <t>'+9.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
         <v>128</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>64980672965</v>
+        <v>66072966115</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1351000</v>
+        <v>1356000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+6.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G6" t="n">
-        <v>1528</v>
+        <v>1544</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2426483646000</v>
+        <v>2478894092500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62500</v>
+        <v>222250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.52%</t>
+          <t>'+4.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="G7" t="n">
-        <v>783</v>
+        <v>1326</v>
       </c>
       <c r="H7" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K7" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L7" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M7" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N7" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>195820599050</v>
+        <v>1761583227500</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>195000</v>
+        <v>1019000</v>
       </c>
       <c r="S7" t="n">
-        <v>15000</v>
+        <v>432000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>중동발 지정학적 리스크 속에서도 삼성그룹주 중 저평가 메리트 부각. MSCI 종목 편입 기대감과 함께 대형 수주 공시 가능성이 거론되며, 외인 매수세 유입 및 야간 선물 급등 등 긍정적 시그널이 다수 관찰됨.</t>
+          <t>트럼프 외교 관련 언급 및 이재명 지지 글 다수. SK하이닉스 ETF 퇴장 및 HBM 부족 뉴스 언급. 외인 매도 시작과 종가 하락 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['저평가', '대형수주', 'MSCI']</t>
+          <t>['공매도', 'HBM', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>222000</v>
+        <v>62300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>133</v>
       </c>
       <c r="F8" t="n">
-        <v>463</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
-        <v>1327</v>
+        <v>806</v>
       </c>
       <c r="H8" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K8" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L8" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>221000</v>
+        <v>60100</v>
       </c>
       <c r="N8" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>1737083094250</v>
+        <v>198738594300</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>1019000</v>
+        <v>195000</v>
       </c>
       <c r="S8" t="n">
-        <v>432000</v>
+        <v>15000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 기대 속 외국인 매도세 지속. 일부 HBM 부족 우려 제기.</t>
+          <t>삼성그룹주 중 저평가 및 MSCI 종목 편입 기대감. 중동 사태 영향 및 대형 수주 공시 가능성 언급. 야간 선물 급등 및 외인 매수세 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', 'HBM', '외국인']</t>
+          <t>['저평가', 'MSCI', '대형수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14640</v>
+        <v>14660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.95%</t>
+          <t>'+3.09%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H9" t="n">
         <v>10.02</v>
@@ -1254,7 +1254,7 @@
         <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>34421633620</v>
+        <v>34654020405</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 영업이익 223% 폭증 실적 발표. 외국인, 기관 프로그램 매수세 유입 확인.</t>
+          <t>223% 영업이익 증가 실적 발표. AI 수혜주 언급 및 공매도/대차 물량 출회 전망. 도배글 신고 및 주가 하락 우려 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익 폭증', '실적 발표', '기관 매수']</t>
+          <t>['영업이익', 'AI', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13690</v>
+        <v>13720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>54668830700</v>
+        <v>55238883050</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16490</v>
+        <v>16510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.17%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>32209485060</v>
+        <v>32639689560</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1498,13 +1498,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="H12" t="n">
         <v>12.32</v>
@@ -1530,7 +1530,7 @@
         <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>38150928600</v>
+        <v>38648770300</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14450</v>
+        <v>14500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G13" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>71505295565</v>
+        <v>72050685655</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34250</v>
+        <v>35050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.16%</t>
+          <t>'-3.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>95455327925</v>
+        <v>98014386225</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>영업이익 증가에도 불구하고 주가 하락 및 개인 투자자들의 불안감 표출. 하락 이유에 대한 불확실성 존재.</t>
+          <t>전년비 157% 영업이익 상승에도 불구하고 주가 하락. 외인 매도 및 프로그램 매수세 부재. 컨센서스 미달 및 하한가 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '주가하락', '개미']</t>
+          <t>['영업이익', '외인', '하한가']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_12.xlsx
+++ b/data/trending_integrated_20261027_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41868943430</v>
+        <v>41875117130</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -676,7 +676,7 @@
         <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18723239545</v>
+        <v>18725785955</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 메인 카메라 단독 공급망 확정, LG이노텍 제치고 채택. 3분기 어닝 서프라이즈 및 텐버거 기대감.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 독점 공급. 3D 센싱 카메라 기술력 기반 텐버거 기대. 3분기 실적 어닝 서프라이즈 가능성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['아틀라스', '로봇', '3D센싱']</t>
+          <t>['아틀라스', '3D센싱', '실적']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2235</v>
+        <v>20650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.83%</t>
+          <t>'+8.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="H4" t="n">
-        <v>4.89</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2035</v>
+        <v>19050</v>
       </c>
       <c r="K4" t="n">
-        <v>2035</v>
+        <v>19450</v>
       </c>
       <c r="L4" t="n">
-        <v>2300</v>
+        <v>22450</v>
       </c>
       <c r="M4" t="n">
-        <v>1953</v>
+        <v>18430</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>41593646207</v>
+        <v>66651114565</v>
       </c>
       <c r="P4" t="n">
-        <v>4980</v>
+        <v>62100</v>
       </c>
       <c r="Q4" t="n">
-        <v>749</v>
+        <v>14600</v>
       </c>
       <c r="R4" t="n">
-        <v>-89000</v>
+        <v>7000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 관련주로 스마트 팩토리 및 자동화 테마 언급. 2026 로보월드 행사 기대감 있으나, 개미 털기 및 변동성 수반 장세 우려.</t>
+          <t>로봇 기업 빅웨이브 관련 기대감 있으나, 상승 여력 및 주가 흐름에 대한 불확실성 존재. 보호예수 물량 및 단타 매매 성향 강함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스마트팩토리', '로보월드', '변동성']</t>
+          <t>['로봇 기업', '상승 여력', '보호예수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20900</v>
+        <v>2200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.71%</t>
+          <t>'+8.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K5" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L5" t="n">
-        <v>22450</v>
+        <v>2300</v>
       </c>
       <c r="M5" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N5" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>66072966115</v>
+        <v>43433469762</v>
       </c>
       <c r="P5" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q5" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R5" t="n">
-        <v>7000</v>
+        <v>-89000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 기업 빅웨이브 관련 기대감 있으나, 상승 여력 및 주가 흐름에 대한 불확실성 존재. 보호예수 물량 및 단타 매매 성향 강함.</t>
+          <t>스마트 팩토리 및 공장 자동화 관련 기대감. 로봇 관련 전시회(로봇월드) 일정 언급. 주가 변동성 및 개미 털기 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇 기업', '상승 여력', '보호예수']</t>
+          <t>['스마트팩토리', '로봇월드', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1356000</v>
+        <v>1354000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.35%</t>
+          <t>'+6.20%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G6" t="n">
-        <v>1544</v>
+        <v>1568</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2478894092500</v>
+        <v>2508104860000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222250</v>
+        <v>62400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.34%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>132</v>
       </c>
       <c r="F7" t="n">
-        <v>461</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>1326</v>
+        <v>809</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K7" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L7" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M7" t="n">
-        <v>221000</v>
+        <v>60100</v>
       </c>
       <c r="N7" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O7" t="n">
-        <v>1761583227500</v>
+        <v>202391571200</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>1019000</v>
+        <v>195000</v>
       </c>
       <c r="S7" t="n">
-        <v>432000</v>
+        <v>15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>트럼프 외교 관련 언급 및 이재명 지지 글 다수. SK하이닉스 ETF 퇴장 및 HBM 부족 뉴스 언급. 외인 매도 시작과 종가 하락 전망.</t>
+          <t>삼성그룹주 중 저평가 분석 및 MSCI 편입 기대감. 중동 전쟁 관련 불확실성 속 공매도 공세. 수주 공시 시 급등 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', 'HBM', '외인']</t>
+          <t>['저평가', 'MSCI', '수주공시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62300</v>
+        <v>222000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>133</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>88</v>
+        <v>463</v>
       </c>
       <c r="G8" t="n">
-        <v>806</v>
+        <v>1296</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>198738594300</v>
+        <v>1784420592750</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>195000</v>
+        <v>1019000</v>
       </c>
       <c r="S8" t="n">
-        <v>15000</v>
+        <v>432000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성그룹주 중 저평가 및 MSCI 종목 편입 기대감. 중동 사태 영향 및 대형 수주 공시 가능성 언급. 야간 선물 급등 및 외인 매수세 기대.</t>
+          <t>대통령 외교 활동 및 SK하이닉스 ETF 퇴장 관련 논란. 엔트로픽 HBM 부족 우려 및 외인 매도세 지속. 실적 및 주주환원 발표 기대감 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['저평가', 'MSCI', '대형수주']</t>
+          <t>['HBM', '외인매도', '실적발표']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14660</v>
+        <v>14670</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.09%</t>
+          <t>'+3.16%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="H9" t="n">
         <v>10.02</v>
@@ -1254,7 +1254,7 @@
         <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>34654020405</v>
+        <v>34897148445</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>223% 영업이익 증가 실적 발표. AI 수혜주 언급 및 공매도/대차 물량 출회 전망. 도배글 신고 및 주가 하락 우려 공존.</t>
+          <t>영업이익 223% 증가 등 호실적 발표. AI 최종 수혜주 가능성 언급. 도배글 및 투자 주의 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익', 'AI', '공매도']</t>
+          <t>['영업이익', 'AI 수혜주', '실적발표']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13720</v>
+        <v>13740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>55238883050</v>
+        <v>55640048450</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16510</v>
+        <v>16520</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+1.35%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>32639689560</v>
+        <v>33122627080</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1498,13 +1498,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="H12" t="n">
         <v>12.32</v>
@@ -1530,7 +1530,7 @@
         <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>38648770300</v>
+        <v>39014480250</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14500</v>
+        <v>14565</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G13" t="n">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>72050685655</v>
+        <v>72870183115</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>의료 AI 대장주로서 성장성 및 확장성 부각. 해외 수출 및 신약 개발 활용 등 긍정적 분석. 연기금 매수세 및 공매도 숏커버링 언급.</t>
+          <t>해외 수출 및 신약 개발 활용 기반 성장성 및 확장성 확고. 루닛스코프, AI 신약 개발 활용. 공매도 숏커버링 및 중요한 날짜 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['의료AI', '성장성', '신약개발']</t>
+          <t>['AI신약개발', '수출', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35050</v>
+        <v>35000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.97%</t>
+          <t>'-4.11%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>98014386225</v>
+        <v>100114732700</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
